--- a/EIS/AB_BM.xlsx
+++ b/EIS/AB_BM.xlsx
@@ -1,42 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\My Drive\KAIST MASc 2021\Laboratory Work\Protocol\overpotential calculation\For paper SI\EIS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AF42E0-624F-461B-A814-FC8DCD04FC58}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17655" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>x1</t>
   </si>
   <si>
     <t>y1</t>
   </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>y2</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>y3</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>y4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -44,15 +56,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -91,26 +96,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -157,7 +153,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -189,27 +185,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -241,24 +219,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -434,688 +394,2195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F84"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H84"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
-        <v>3.866E-2</v>
+        <v>0.03866</v>
       </c>
       <c r="B2">
-        <v>-5.2659999999999998E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.05266</v>
+      </c>
+      <c r="C2">
+        <v>0.03820298707929683</v>
+      </c>
+      <c r="D2">
+        <v>-0.0558196</v>
+      </c>
+      <c r="E2">
+        <v>0.03889653382721247</v>
+      </c>
+      <c r="F2">
+        <v>-0.0510802</v>
+      </c>
+      <c r="G2">
+        <v>0.03896156291354555</v>
+      </c>
+      <c r="H2">
+        <v>-0.0542398</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
-        <v>3.7850000000000002E-2</v>
+        <v>0.03785</v>
       </c>
       <c r="B3">
-        <v>-4.8379999999999999E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.04838</v>
+      </c>
+      <c r="C3">
+        <v>0.03746542944050418</v>
+      </c>
+      <c r="D3">
+        <v>-0.0512828</v>
+      </c>
+      <c r="E3">
+        <v>0.03804904020685198</v>
+      </c>
+      <c r="F3">
+        <v>-0.0469286</v>
+      </c>
+      <c r="G3">
+        <v>0.03810376135582111</v>
+      </c>
+      <c r="H3">
+        <v>-0.0498314</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
-        <v>3.7600000000000001E-2</v>
+        <v>0.0376</v>
       </c>
       <c r="B4">
-        <v>-4.3610000000000003E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.04361</v>
+      </c>
+      <c r="C4">
+        <v>0.03723778819396324</v>
+      </c>
+      <c r="D4">
+        <v>-0.04622660000000001</v>
+      </c>
+      <c r="E4">
+        <v>0.03778746810180245</v>
+      </c>
+      <c r="F4">
+        <v>-0.0423017</v>
+      </c>
+      <c r="G4">
+        <v>0.0378390077886222</v>
+      </c>
+      <c r="H4">
+        <v>-0.0449183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
-        <v>3.6880000000000003E-2</v>
+        <v>0.03688</v>
       </c>
       <c r="B5">
-        <v>-3.9600000000000003E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.0396</v>
+      </c>
+      <c r="C5">
+        <v>0.03658218140392534</v>
+      </c>
+      <c r="D5">
+        <v>-0.04197600000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.03703414043925979</v>
+      </c>
+      <c r="F5">
+        <v>-0.038412</v>
+      </c>
+      <c r="G5">
+        <v>0.03707651751508937</v>
+      </c>
+      <c r="H5">
+        <v>-0.040788</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
-        <v>3.6510000000000001E-2</v>
+        <v>0.03651</v>
       </c>
       <c r="B6">
-        <v>-3.5709999999999999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.03571</v>
+      </c>
+      <c r="C6">
+        <v>0.03624527235904474</v>
+      </c>
+      <c r="D6">
+        <v>-0.0378526</v>
+      </c>
+      <c r="E6">
+        <v>0.03664701372378648</v>
+      </c>
+      <c r="F6">
+        <v>-0.03463869999999999</v>
+      </c>
+      <c r="G6">
+        <v>0.036684682235635</v>
+      </c>
+      <c r="H6">
+        <v>-0.0367813</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
-        <v>3.6130000000000002E-2</v>
+        <v>0.03613</v>
       </c>
       <c r="B7">
-        <v>-3.2390000000000002E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.03239</v>
+      </c>
+      <c r="C7">
+        <v>0.03589925766430251</v>
+      </c>
+      <c r="D7">
+        <v>-0.03433340000000001</v>
+      </c>
+      <c r="E7">
+        <v>0.03624942412411118</v>
+      </c>
+      <c r="F7">
+        <v>-0.0314183</v>
+      </c>
+      <c r="G7">
+        <v>0.03628225681349267</v>
+      </c>
+      <c r="H7">
+        <v>-0.0333617</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
-        <v>3.5880000000000002E-2</v>
+        <v>0.03588</v>
       </c>
       <c r="B8">
-        <v>-2.9159999999999998E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.02916</v>
+      </c>
+      <c r="C8">
+        <v>0.03567161641776157</v>
+      </c>
+      <c r="D8">
+        <v>-0.0309096</v>
+      </c>
+      <c r="E8">
+        <v>0.03598785201906165</v>
+      </c>
+      <c r="F8">
+        <v>-0.0282852</v>
+      </c>
+      <c r="G8">
+        <v>0.03601750324629377</v>
+      </c>
+      <c r="H8">
+        <v>-0.0300348</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
-        <v>3.5619999999999999E-2</v>
+        <v>0.03562</v>
       </c>
       <c r="B9">
-        <v>-2.6169999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.02617</v>
+      </c>
+      <c r="C9">
+        <v>0.03543486952135899</v>
+      </c>
+      <c r="D9">
+        <v>-0.0277402</v>
+      </c>
+      <c r="E9">
+        <v>0.03571581702981014</v>
+      </c>
+      <c r="F9">
+        <v>-0.0253849</v>
+      </c>
+      <c r="G9">
+        <v>0.0357421595364069</v>
+      </c>
+      <c r="H9">
+        <v>-0.0269551</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
-        <v>3.5450000000000002E-2</v>
+        <v>0.03545</v>
       </c>
       <c r="B10">
-        <v>-2.366E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.02366</v>
+      </c>
+      <c r="C10">
+        <v>0.03528007347371116</v>
+      </c>
+      <c r="D10">
+        <v>-0.0250796</v>
+      </c>
+      <c r="E10">
+        <v>0.03553794799837645</v>
+      </c>
+      <c r="F10">
+        <v>-0.0229502</v>
+      </c>
+      <c r="G10">
+        <v>0.03556212711071165</v>
+      </c>
+      <c r="H10">
+        <v>-0.0243698</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
-        <v>3.5249999999999997E-2</v>
+        <v>0.03525</v>
       </c>
       <c r="B11">
-        <v>-2.1430000000000001E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.02143</v>
+      </c>
+      <c r="C11">
+        <v>0.0350979604764784</v>
+      </c>
+      <c r="D11">
+        <v>-0.0227158</v>
+      </c>
+      <c r="E11">
+        <v>0.03532869031433682</v>
+      </c>
+      <c r="F11">
+        <v>-0.0207871</v>
+      </c>
+      <c r="G11">
+        <v>0.03535032425695252</v>
+      </c>
+      <c r="H11">
+        <v>-0.0220729</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12">
-        <v>3.508E-2</v>
+        <v>0.03508</v>
       </c>
       <c r="B12">
-        <v>-1.9439999999999999E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.01944</v>
+      </c>
+      <c r="C12">
+        <v>0.03494316442883056</v>
+      </c>
+      <c r="D12">
+        <v>-0.0206064</v>
+      </c>
+      <c r="E12">
+        <v>0.03515082128290314</v>
+      </c>
+      <c r="F12">
+        <v>-0.0188568</v>
+      </c>
+      <c r="G12">
+        <v>0.03517029183125728</v>
+      </c>
+      <c r="H12">
+        <v>-0.0200232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13">
-        <v>3.4909999999999997E-2</v>
+        <v>0.03491</v>
       </c>
       <c r="B13">
-        <v>-1.7559999999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.01756</v>
+      </c>
+      <c r="C13">
+        <v>0.03478836838118272</v>
+      </c>
+      <c r="D13">
+        <v>-0.0186136</v>
+      </c>
+      <c r="E13">
+        <v>0.03497295225146945</v>
+      </c>
+      <c r="F13">
+        <v>-0.0170332</v>
+      </c>
+      <c r="G13">
+        <v>0.03499025940556202</v>
+      </c>
+      <c r="H13">
+        <v>-0.0180868</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14">
-        <v>3.4729999999999997E-2</v>
+        <v>0.03473</v>
       </c>
       <c r="B14">
-        <v>-1.5890000000000001E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.01589</v>
+      </c>
+      <c r="C14">
+        <v>0.03462446668367324</v>
+      </c>
+      <c r="D14">
+        <v>-0.0168434</v>
+      </c>
+      <c r="E14">
+        <v>0.0347846203358338</v>
+      </c>
+      <c r="F14">
+        <v>-0.0154133</v>
+      </c>
+      <c r="G14">
+        <v>0.03479963683717882</v>
+      </c>
+      <c r="H14">
+        <v>-0.0163667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15">
-        <v>3.4590000000000003E-2</v>
+        <v>0.03459</v>
       </c>
       <c r="B15">
-        <v>-1.431E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-0.01431</v>
+      </c>
+      <c r="C15">
+        <v>0.03449698758561032</v>
+      </c>
+      <c r="D15">
+        <v>-0.0151686</v>
+      </c>
+      <c r="E15">
+        <v>0.03463813995700606</v>
+      </c>
+      <c r="F15">
+        <v>-0.0138807</v>
+      </c>
+      <c r="G15">
+        <v>0.03465137483954743</v>
+      </c>
+      <c r="H15">
+        <v>-0.0147393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16">
-        <v>3.4130000000000001E-2</v>
+        <v>0.03413</v>
       </c>
       <c r="B16">
-        <v>-1.2630000000000001E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.01263</v>
+      </c>
+      <c r="C16">
+        <v>0.03407812769197498</v>
+      </c>
+      <c r="D16">
+        <v>-0.0133878</v>
+      </c>
+      <c r="E16">
+        <v>0.03415684728371492</v>
+      </c>
+      <c r="F16">
+        <v>-0.0122511</v>
+      </c>
+      <c r="G16">
+        <v>0.03416422827590145</v>
+      </c>
+      <c r="H16">
+        <v>-0.0130089</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
-        <v>3.3980000000000003E-2</v>
+        <v>0.03398</v>
       </c>
       <c r="B17">
-        <v>-1.137E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.01137</v>
+      </c>
+      <c r="C17">
+        <v>0.03394154294405042</v>
+      </c>
+      <c r="D17">
+        <v>-0.0120522</v>
+      </c>
+      <c r="E17">
+        <v>0.0339999040206852</v>
+      </c>
+      <c r="F17">
+        <v>-0.0110289</v>
+      </c>
+      <c r="G17">
+        <v>0.0340053761355821</v>
+      </c>
+      <c r="H17">
+        <v>-0.0117111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
-        <v>3.3820000000000003E-2</v>
+        <v>0.03382</v>
       </c>
       <c r="B18">
-        <v>-9.9799999999999993E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.009979999999999999</v>
+      </c>
+      <c r="C18">
+        <v>0.03379585254626422</v>
+      </c>
+      <c r="D18">
+        <v>-0.0105788</v>
+      </c>
+      <c r="E18">
+        <v>0.0338324978734535</v>
+      </c>
+      <c r="F18">
+        <v>-0.009680599999999999</v>
+      </c>
+      <c r="G18">
+        <v>0.03383593385257481</v>
+      </c>
+      <c r="H18">
+        <v>-0.0102794</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19">
-        <v>3.3619999999999997E-2</v>
+        <v>0.03362</v>
       </c>
       <c r="B19">
-        <v>-8.77E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00877</v>
+      </c>
+      <c r="C19">
+        <v>0.03361373954903146</v>
+      </c>
+      <c r="D19">
+        <v>-0.009296200000000001</v>
+      </c>
+      <c r="E19">
+        <v>0.03362324018941386</v>
+      </c>
+      <c r="F19">
+        <v>-0.0085069</v>
+      </c>
+      <c r="G19">
+        <v>0.03362413099881568</v>
+      </c>
+      <c r="H19">
+        <v>-0.009033100000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20">
-        <v>3.3550000000000003E-2</v>
+        <v>0.03355</v>
       </c>
       <c r="B20">
-        <v>-7.5399999999999998E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00754</v>
+      </c>
+      <c r="C20">
+        <v>0.03355</v>
+      </c>
+      <c r="D20">
+        <v>-0.0079924</v>
+      </c>
+      <c r="E20">
+        <v>0.03355</v>
+      </c>
+      <c r="F20">
+        <v>-0.0073138</v>
+      </c>
+      <c r="G20">
+        <v>0.03355</v>
+      </c>
+      <c r="H20">
+        <v>-0.0077662</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
-        <v>3.3570000000000003E-2</v>
+        <v>0.03357</v>
       </c>
       <c r="B21">
-        <v>-6.3299999999999997E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00633</v>
+      </c>
+      <c r="C21">
+        <v>0.03356821129972327</v>
+      </c>
+      <c r="D21">
+        <v>-0.0067098</v>
+      </c>
+      <c r="E21">
+        <v>0.03357092576840397</v>
+      </c>
+      <c r="F21">
+        <v>-0.0061401</v>
+      </c>
+      <c r="G21">
+        <v>0.03357118028537592</v>
+      </c>
+      <c r="H21">
+        <v>-0.006519899999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22">
-        <v>3.3649999999999999E-2</v>
+        <v>0.03365</v>
       </c>
       <c r="B22">
-        <v>-5.3299999999999997E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00533</v>
+      </c>
+      <c r="C22">
+        <v>0.03364105649861637</v>
+      </c>
+      <c r="D22">
+        <v>-0.0056498</v>
+      </c>
+      <c r="E22">
+        <v>0.03365462884201981</v>
+      </c>
+      <c r="F22">
+        <v>-0.0051701</v>
+      </c>
+      <c r="G22">
+        <v>0.03365590142687957</v>
+      </c>
+      <c r="H22">
+        <v>-0.0054899</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
-        <v>3.3739999999999999E-2</v>
+        <v>0.03374</v>
       </c>
       <c r="B23">
-        <v>-4.5599999999999998E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00456</v>
+      </c>
+      <c r="C23">
+        <v>0.03372300734737112</v>
+      </c>
+      <c r="D23">
+        <v>-0.0048336</v>
+      </c>
+      <c r="E23">
+        <v>0.03374879479983765</v>
+      </c>
+      <c r="F23">
+        <v>-0.0044232</v>
+      </c>
+      <c r="G23">
+        <v>0.03375121271107116</v>
+      </c>
+      <c r="H23">
+        <v>-0.0046968</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
-        <v>3.3759999999999998E-2</v>
+        <v>0.03376</v>
       </c>
       <c r="B24">
-        <v>-3.8999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.0039</v>
+      </c>
+      <c r="C24">
+        <v>0.03374121864709439</v>
+      </c>
+      <c r="D24">
+        <v>-0.004134</v>
+      </c>
+      <c r="E24">
+        <v>0.0337697205682416</v>
+      </c>
+      <c r="F24">
+        <v>-0.003783</v>
+      </c>
+      <c r="G24">
+        <v>0.03377239299644708</v>
+      </c>
+      <c r="H24">
+        <v>-0.004017</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
-        <v>3.3770000000000001E-2</v>
+        <v>0.03377</v>
       </c>
       <c r="B25">
-        <v>-3.2100000000000002E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00321</v>
+      </c>
+      <c r="C25">
+        <v>0.03375032429695603</v>
+      </c>
+      <c r="D25">
+        <v>-0.0034026</v>
+      </c>
+      <c r="E25">
+        <v>0.03378018345244359</v>
+      </c>
+      <c r="F25">
+        <v>-0.0031137</v>
+      </c>
+      <c r="G25">
+        <v>0.03378298313913503</v>
+      </c>
+      <c r="H25">
+        <v>-0.0033063</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
-        <v>3.3790000000000001E-2</v>
+        <v>0.03379</v>
       </c>
       <c r="B26">
-        <v>-2.5699999999999998E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00257</v>
+      </c>
+      <c r="C26">
+        <v>0.03376853559667931</v>
+      </c>
+      <c r="D26">
+        <v>-0.0027242</v>
+      </c>
+      <c r="E26">
+        <v>0.03380110922084756</v>
+      </c>
+      <c r="F26">
+        <v>-0.0024929</v>
+      </c>
+      <c r="G26">
+        <v>0.03380416342451095</v>
+      </c>
+      <c r="H26">
+        <v>-0.0026471</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
-        <v>3.3820000000000003E-2</v>
+        <v>0.03382</v>
       </c>
       <c r="B27">
-        <v>-1.97E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00197</v>
+      </c>
+      <c r="C27">
+        <v>0.03379585254626422</v>
+      </c>
+      <c r="D27">
+        <v>-0.0020882</v>
+      </c>
+      <c r="E27">
+        <v>0.0338324978734535</v>
+      </c>
+      <c r="F27">
+        <v>-0.0019109</v>
+      </c>
+      <c r="G27">
+        <v>0.03383593385257481</v>
+      </c>
+      <c r="H27">
+        <v>-0.0020291</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
-        <v>3.3829999999999999E-2</v>
+        <v>0.03383</v>
       </c>
       <c r="B28">
-        <v>-1.3699999999999999E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>-0.00137</v>
+      </c>
+      <c r="C28">
+        <v>0.03380495819612585</v>
+      </c>
+      <c r="D28">
+        <v>-0.0014522</v>
+      </c>
+      <c r="E28">
+        <v>0.03384296075765548</v>
+      </c>
+      <c r="F28">
+        <v>-0.0013289</v>
+      </c>
+      <c r="G28">
+        <v>0.03384652399526277</v>
+      </c>
+      <c r="H28">
+        <v>-0.0014111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29">
-        <v>3.3860000000000001E-2</v>
-      </c>
-      <c r="B29" s="2">
-        <v>-7.86501E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.03386</v>
+      </c>
+      <c r="B29">
+        <v>-0.000786501</v>
+      </c>
+      <c r="C29">
+        <v>0.03383227514571076</v>
+      </c>
+      <c r="D29">
+        <v>-0.00083369106</v>
+      </c>
+      <c r="E29">
+        <v>0.03387434941026141</v>
+      </c>
+      <c r="F29">
+        <v>-0.0007629059699999999</v>
+      </c>
+      <c r="G29">
+        <v>0.03387829442332664</v>
+      </c>
+      <c r="H29">
+        <v>-0.00081009603</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
-        <v>3.3890000000000003E-2</v>
-      </c>
-      <c r="B30" s="2">
-        <v>-2.2156899999999999E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.03389</v>
+      </c>
+      <c r="B30">
+        <v>-0.000221569</v>
+      </c>
+      <c r="C30">
+        <v>0.03385959209529568</v>
+      </c>
+      <c r="D30">
+        <v>-0.00023486314</v>
+      </c>
+      <c r="E30">
+        <v>0.03390573806286737</v>
+      </c>
+      <c r="F30">
+        <v>-0.00021492193</v>
+      </c>
+      <c r="G30">
+        <v>0.0339100648513905</v>
+      </c>
+      <c r="H30">
+        <v>-0.00022821607</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31">
-        <v>3.3939999999999998E-2</v>
-      </c>
-      <c r="B31" s="2">
-        <v>2.99241E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.03394</v>
+      </c>
+      <c r="B31">
+        <v>0.000299241</v>
+      </c>
+      <c r="C31">
+        <v>0.03390512034460386</v>
+      </c>
+      <c r="D31">
+        <v>0.00031719546</v>
+      </c>
+      <c r="E31">
+        <v>0.03395805248387727</v>
+      </c>
+      <c r="F31">
+        <v>0.00029026377</v>
+      </c>
+      <c r="G31">
+        <v>0.03396301556483027</v>
+      </c>
+      <c r="H31">
+        <v>0.00030821823</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="B32" s="2">
-        <v>7.9927600000000002E-4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.034</v>
+      </c>
+      <c r="B32">
+        <v>0.000799276</v>
+      </c>
+      <c r="C32">
+        <v>0.0339597542437737</v>
+      </c>
+      <c r="D32">
+        <v>0.0008472325600000001</v>
+      </c>
+      <c r="E32">
+        <v>0.03402082978908916</v>
+      </c>
+      <c r="F32">
+        <v>0.00077529772</v>
+      </c>
+      <c r="G32">
+        <v>0.03402655642095802</v>
+      </c>
+      <c r="H32">
+        <v>0.00082325428</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33">
-        <v>3.406E-2</v>
+        <v>0.03406</v>
       </c>
       <c r="B33">
-        <v>1.2999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.0013</v>
+      </c>
+      <c r="C33">
+        <v>0.03401438814294352</v>
+      </c>
+      <c r="D33">
+        <v>0.001378</v>
+      </c>
+      <c r="E33">
+        <v>0.03408360709430105</v>
+      </c>
+      <c r="F33">
+        <v>0.001261</v>
+      </c>
+      <c r="G33">
+        <v>0.03409009727708576</v>
+      </c>
+      <c r="H33">
+        <v>0.001339</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34">
-        <v>3.4130000000000001E-2</v>
+        <v>0.03413</v>
       </c>
       <c r="B34">
-        <v>1.7700000000000001E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00177</v>
+      </c>
+      <c r="C34">
+        <v>0.03407812769197498</v>
+      </c>
+      <c r="D34">
+        <v>0.0018762</v>
+      </c>
+      <c r="E34">
+        <v>0.03415684728371492</v>
+      </c>
+      <c r="F34">
+        <v>0.0017169</v>
+      </c>
+      <c r="G34">
+        <v>0.03416422827590145</v>
+      </c>
+      <c r="H34">
+        <v>0.0018231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35">
-        <v>3.4209999999999997E-2</v>
+        <v>0.03421</v>
       </c>
       <c r="B35">
-        <v>2.2499999999999998E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00225</v>
+      </c>
+      <c r="C35">
+        <v>0.03415097289086808</v>
+      </c>
+      <c r="D35">
+        <v>0.002385</v>
+      </c>
+      <c r="E35">
+        <v>0.03424055035733076</v>
+      </c>
+      <c r="F35">
+        <v>0.0021825</v>
+      </c>
+      <c r="G35">
+        <v>0.03424894941740509</v>
+      </c>
+      <c r="H35">
+        <v>0.0023175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36">
-        <v>3.4290000000000001E-2</v>
+        <v>0.03429</v>
       </c>
       <c r="B36">
-        <v>2.7100000000000002E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00271</v>
+      </c>
+      <c r="C36">
+        <v>0.03422381808976119</v>
+      </c>
+      <c r="D36">
+        <v>0.0028726</v>
+      </c>
+      <c r="E36">
+        <v>0.03432425343094662</v>
+      </c>
+      <c r="F36">
+        <v>0.0026287</v>
+      </c>
+      <c r="G36">
+        <v>0.03433367055890874</v>
+      </c>
+      <c r="H36">
+        <v>0.0027913</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37">
-        <v>3.4369999999999998E-2</v>
+        <v>0.03437</v>
       </c>
       <c r="B37">
-        <v>3.1800000000000001E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00318</v>
+      </c>
+      <c r="C37">
+        <v>0.03429666328865429</v>
+      </c>
+      <c r="D37">
+        <v>0.0033708</v>
+      </c>
+      <c r="E37">
+        <v>0.03440795650456247</v>
+      </c>
+      <c r="F37">
+        <v>0.0030846</v>
+      </c>
+      <c r="G37">
+        <v>0.03441839170041239</v>
+      </c>
+      <c r="H37">
+        <v>0.0032754</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38">
-        <v>3.4450000000000001E-2</v>
+        <v>0.03445</v>
       </c>
       <c r="B38">
-        <v>3.65E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00365</v>
+      </c>
+      <c r="C38">
+        <v>0.03436950848754739</v>
+      </c>
+      <c r="D38">
+        <v>0.003869</v>
+      </c>
+      <c r="E38">
+        <v>0.03449165957817832</v>
+      </c>
+      <c r="F38">
+        <v>0.0035405</v>
+      </c>
+      <c r="G38">
+        <v>0.03450311284191605</v>
+      </c>
+      <c r="H38">
+        <v>0.0037595</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39">
-        <v>3.4540000000000001E-2</v>
+        <v>0.03454</v>
       </c>
       <c r="B39">
-        <v>4.1399999999999996E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00414</v>
+      </c>
+      <c r="C39">
+        <v>0.03445145933630213</v>
+      </c>
+      <c r="D39">
+        <v>0.0043884</v>
+      </c>
+      <c r="E39">
+        <v>0.03458582553599615</v>
+      </c>
+      <c r="F39">
+        <v>0.004015799999999999</v>
+      </c>
+      <c r="G39">
+        <v>0.03459842412610765</v>
+      </c>
+      <c r="H39">
+        <v>0.0042642</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40">
-        <v>3.4630000000000001E-2</v>
+        <v>0.03463</v>
       </c>
       <c r="B40">
-        <v>4.6499999999999996E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00465</v>
+      </c>
+      <c r="C40">
+        <v>0.03453341018505687</v>
+      </c>
+      <c r="D40">
+        <v>0.004929</v>
+      </c>
+      <c r="E40">
+        <v>0.03467999149381399</v>
+      </c>
+      <c r="F40">
+        <v>0.0045105</v>
+      </c>
+      <c r="G40">
+        <v>0.03469373541029926</v>
+      </c>
+      <c r="H40">
+        <v>0.004789499999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41">
-        <v>3.4720000000000001E-2</v>
+        <v>0.03472</v>
       </c>
       <c r="B41">
-        <v>5.1999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.0052</v>
+      </c>
+      <c r="C41">
+        <v>0.0346153610338116</v>
+      </c>
+      <c r="D41">
+        <v>0.005512</v>
+      </c>
+      <c r="E41">
+        <v>0.03477415745163182</v>
+      </c>
+      <c r="F41">
+        <v>0.005044</v>
+      </c>
+      <c r="G41">
+        <v>0.03478904669449086</v>
+      </c>
+      <c r="H41">
+        <v>0.005356</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42">
-        <v>3.4819999999999997E-2</v>
+        <v>0.03482</v>
       </c>
       <c r="B42">
-        <v>5.77E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00577</v>
+      </c>
+      <c r="C42">
+        <v>0.03470641753242798</v>
+      </c>
+      <c r="D42">
+        <v>0.0061162</v>
+      </c>
+      <c r="E42">
+        <v>0.03487878629365163</v>
+      </c>
+      <c r="F42">
+        <v>0.0055969</v>
+      </c>
+      <c r="G42">
+        <v>0.03489494812137042</v>
+      </c>
+      <c r="H42">
+        <v>0.0059431</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43">
-        <v>3.49E-2</v>
+        <v>0.0349</v>
       </c>
       <c r="B43">
-        <v>6.3899999999999998E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00639</v>
+      </c>
+      <c r="C43">
+        <v>0.03477926273132108</v>
+      </c>
+      <c r="D43">
+        <v>0.006773400000000001</v>
+      </c>
+      <c r="E43">
+        <v>0.03496248936726747</v>
+      </c>
+      <c r="F43">
+        <v>0.006198299999999999</v>
+      </c>
+      <c r="G43">
+        <v>0.03497966926287407</v>
+      </c>
+      <c r="H43">
+        <v>0.0065817</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="B44">
-        <v>7.0600000000000003E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00706</v>
+      </c>
+      <c r="C44">
+        <v>0.03487031922993746</v>
+      </c>
+      <c r="D44">
+        <v>0.007483600000000001</v>
+      </c>
+      <c r="E44">
+        <v>0.0350671182092873</v>
+      </c>
+      <c r="F44">
+        <v>0.0068482</v>
+      </c>
+      <c r="G44">
+        <v>0.03508557068975363</v>
+      </c>
+      <c r="H44">
+        <v>0.0072718</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45">
-        <v>3.5099999999999999E-2</v>
+        <v>0.0351</v>
       </c>
       <c r="B45">
-        <v>7.79E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00779</v>
+      </c>
+      <c r="C45">
+        <v>0.03496137572855383</v>
+      </c>
+      <c r="D45">
+        <v>0.0082574</v>
+      </c>
+      <c r="E45">
+        <v>0.03517174705130711</v>
+      </c>
+      <c r="F45">
+        <v>0.0075563</v>
+      </c>
+      <c r="G45">
+        <v>0.03519147211663318</v>
+      </c>
+      <c r="H45">
+        <v>0.0080237</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46">
-        <v>3.5209999999999998E-2</v>
+        <v>0.03521</v>
       </c>
       <c r="B46">
-        <v>8.5900000000000004E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00859</v>
+      </c>
+      <c r="C46">
+        <v>0.03506153787703185</v>
+      </c>
+      <c r="D46">
+        <v>0.009105400000000001</v>
+      </c>
+      <c r="E46">
+        <v>0.0352868387775289</v>
+      </c>
+      <c r="F46">
+        <v>0.008332300000000001</v>
+      </c>
+      <c r="G46">
+        <v>0.03530796368620071</v>
+      </c>
+      <c r="H46">
+        <v>0.0088477</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47">
-        <v>3.5299999999999998E-2</v>
+        <v>0.0353</v>
       </c>
       <c r="B47">
-        <v>9.4599999999999997E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.00946</v>
+      </c>
+      <c r="C47">
+        <v>0.03514348872578658</v>
+      </c>
+      <c r="D47">
+        <v>0.0100276</v>
+      </c>
+      <c r="E47">
+        <v>0.03538100473534674</v>
+      </c>
+      <c r="F47">
+        <v>0.009176199999999999</v>
+      </c>
+      <c r="G47">
+        <v>0.03540327497039231</v>
+      </c>
+      <c r="H47">
+        <v>0.0097438</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48">
-        <v>3.542E-2</v>
+        <v>0.03542</v>
       </c>
       <c r="B48">
-        <v>1.0410000000000001E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.01041</v>
+      </c>
+      <c r="C48">
+        <v>0.03525275652412624</v>
+      </c>
+      <c r="D48">
+        <v>0.0110346</v>
+      </c>
+      <c r="E48">
+        <v>0.03550655934577051</v>
+      </c>
+      <c r="F48">
+        <v>0.0100977</v>
+      </c>
+      <c r="G48">
+        <v>0.03553035668264778</v>
+      </c>
+      <c r="H48">
+        <v>0.0107223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49">
-        <v>3.5529999999999999E-2</v>
+        <v>0.03553</v>
       </c>
       <c r="B49">
-        <v>1.146E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.01146</v>
+      </c>
+      <c r="C49">
+        <v>0.03535291867260425</v>
+      </c>
+      <c r="D49">
+        <v>0.0121476</v>
+      </c>
+      <c r="E49">
+        <v>0.03562165107199231</v>
+      </c>
+      <c r="F49">
+        <v>0.0111162</v>
+      </c>
+      <c r="G49">
+        <v>0.03564684825221531</v>
+      </c>
+      <c r="H49">
+        <v>0.0118038</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50">
-        <v>3.567E-2</v>
+        <v>0.03567</v>
       </c>
       <c r="B50">
-        <v>1.2630000000000001E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.01263</v>
+      </c>
+      <c r="C50">
+        <v>0.03548039777066718</v>
+      </c>
+      <c r="D50">
+        <v>0.0133878</v>
+      </c>
+      <c r="E50">
+        <v>0.03576813145082005</v>
+      </c>
+      <c r="F50">
+        <v>0.0122511</v>
+      </c>
+      <c r="G50">
+        <v>0.03579511024984668</v>
+      </c>
+      <c r="H50">
+        <v>0.0130089</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51">
-        <v>3.5790000000000002E-2</v>
+        <v>0.03579</v>
       </c>
       <c r="B51">
-        <v>1.393E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.01393</v>
+      </c>
+      <c r="C51">
+        <v>0.03558966556900683</v>
+      </c>
+      <c r="D51">
+        <v>0.0147658</v>
+      </c>
+      <c r="E51">
+        <v>0.03589368606124382</v>
+      </c>
+      <c r="F51">
+        <v>0.0135121</v>
+      </c>
+      <c r="G51">
+        <v>0.03592219196210216</v>
+      </c>
+      <c r="H51">
+        <v>0.0143479</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52">
-        <v>3.5920000000000001E-2</v>
+        <v>0.03592</v>
       </c>
       <c r="B52">
-        <v>1.5350000000000001E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.01535</v>
+      </c>
+      <c r="C52">
+        <v>0.03570803901720812</v>
+      </c>
+      <c r="D52">
+        <v>0.016271</v>
+      </c>
+      <c r="E52">
+        <v>0.03602970355586958</v>
+      </c>
+      <c r="F52">
+        <v>0.0148895</v>
+      </c>
+      <c r="G52">
+        <v>0.03605986381704559</v>
+      </c>
+      <c r="H52">
+        <v>0.0158105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53">
-        <v>3.6080000000000001E-2</v>
+        <v>0.03608</v>
       </c>
       <c r="B53">
-        <v>1.6930000000000001E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.01693</v>
+      </c>
+      <c r="C53">
+        <v>0.03585372941499432</v>
+      </c>
+      <c r="D53">
+        <v>0.0179458</v>
+      </c>
+      <c r="E53">
+        <v>0.03619710970310128</v>
+      </c>
+      <c r="F53">
+        <v>0.0164221</v>
+      </c>
+      <c r="G53">
+        <v>0.03622930610005289</v>
+      </c>
+      <c r="H53">
+        <v>0.0174379</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54">
-        <v>3.6229999999999998E-2</v>
+        <v>0.03623</v>
       </c>
       <c r="B54">
-        <v>1.8689999999999998E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.01869</v>
+      </c>
+      <c r="C54">
+        <v>0.03599031416291888</v>
+      </c>
+      <c r="D54">
+        <v>0.0198114</v>
+      </c>
+      <c r="E54">
+        <v>0.036354052966131</v>
+      </c>
+      <c r="F54">
+        <v>0.0181293</v>
+      </c>
+      <c r="G54">
+        <v>0.03638815824037222</v>
+      </c>
+      <c r="H54">
+        <v>0.0192507</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55">
-        <v>3.6400000000000002E-2</v>
+        <v>0.0364</v>
       </c>
       <c r="B55">
-        <v>2.0650000000000002E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.02065</v>
+      </c>
+      <c r="C55">
+        <v>0.03614511021056672</v>
+      </c>
+      <c r="D55">
+        <v>0.021889</v>
+      </c>
+      <c r="E55">
+        <v>0.03653192199756469</v>
+      </c>
+      <c r="F55">
+        <v>0.0200305</v>
+      </c>
+      <c r="G55">
+        <v>0.03656819066606748</v>
+      </c>
+      <c r="H55">
+        <v>0.0212695</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56">
-        <v>3.6569999999999998E-2</v>
+        <v>0.03657</v>
       </c>
       <c r="B56">
-        <v>2.281E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.02281</v>
+      </c>
+      <c r="C56">
+        <v>0.03629990625821457</v>
+      </c>
+      <c r="D56">
+        <v>0.0241786</v>
+      </c>
+      <c r="E56">
+        <v>0.03670979102899836</v>
+      </c>
+      <c r="F56">
+        <v>0.0221257</v>
+      </c>
+      <c r="G56">
+        <v>0.03674822309176273</v>
+      </c>
+      <c r="H56">
+        <v>0.0234943</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57">
-        <v>3.6760000000000001E-2</v>
+        <v>0.03676</v>
       </c>
       <c r="B57">
-        <v>2.5229999999999999E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.02523</v>
+      </c>
+      <c r="C57">
+        <v>0.03647291360558568</v>
+      </c>
+      <c r="D57">
+        <v>0.0267438</v>
+      </c>
+      <c r="E57">
+        <v>0.03690858582883601</v>
+      </c>
+      <c r="F57">
+        <v>0.0244731</v>
+      </c>
+      <c r="G57">
+        <v>0.03694943580283389</v>
+      </c>
+      <c r="H57">
+        <v>0.0259869</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58">
-        <v>3.6949999999999997E-2</v>
+        <v>0.03695</v>
       </c>
       <c r="B58">
-        <v>2.792E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.02792</v>
+      </c>
+      <c r="C58">
+        <v>0.0366459209529568</v>
+      </c>
+      <c r="D58">
+        <v>0.0295952</v>
+      </c>
+      <c r="E58">
+        <v>0.03710738062867366</v>
+      </c>
+      <c r="F58">
+        <v>0.0270824</v>
+      </c>
+      <c r="G58">
+        <v>0.03715064851390506</v>
+      </c>
+      <c r="H58">
+        <v>0.0287576</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59">
-        <v>3.7179999999999998E-2</v>
+        <v>0.03718</v>
       </c>
       <c r="B59">
-        <v>3.091E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.03091</v>
+      </c>
+      <c r="C59">
+        <v>0.03685535089977446</v>
+      </c>
+      <c r="D59">
+        <v>0.0327646</v>
+      </c>
+      <c r="E59">
+        <v>0.03734802696531922</v>
+      </c>
+      <c r="F59">
+        <v>0.0299827</v>
+      </c>
+      <c r="G59">
+        <v>0.03739422179572806</v>
+      </c>
+      <c r="H59">
+        <v>0.0318373</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60">
-        <v>3.7400000000000003E-2</v>
+        <v>0.0374</v>
       </c>
       <c r="B60">
-        <v>3.4250000000000003E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.03425</v>
+      </c>
+      <c r="C60">
+        <v>0.03705567519673049</v>
+      </c>
+      <c r="D60">
+        <v>0.036305</v>
+      </c>
+      <c r="E60">
+        <v>0.03757821041776282</v>
+      </c>
+      <c r="F60">
+        <v>0.0332225</v>
+      </c>
+      <c r="G60">
+        <v>0.03762720493486309</v>
+      </c>
+      <c r="H60">
+        <v>0.0352775</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61">
-        <v>3.764E-2</v>
+        <v>0.03764</v>
       </c>
       <c r="B61">
-        <v>3.7949999999999998E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.03795</v>
+      </c>
+      <c r="C61">
+        <v>0.03727421079340979</v>
+      </c>
+      <c r="D61">
+        <v>0.040227</v>
+      </c>
+      <c r="E61">
+        <v>0.03782931963861037</v>
+      </c>
+      <c r="F61">
+        <v>0.0368115</v>
+      </c>
+      <c r="G61">
+        <v>0.03788136835937403</v>
+      </c>
+      <c r="H61">
+        <v>0.0390885</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62">
-        <v>3.7909999999999999E-2</v>
+        <v>0.03791</v>
       </c>
       <c r="B62">
-        <v>4.2079999999999999E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.04208</v>
+      </c>
+      <c r="C62">
+        <v>0.03752006333967401</v>
+      </c>
+      <c r="D62">
+        <v>0.0446048</v>
+      </c>
+      <c r="E62">
+        <v>0.03811181751206386</v>
+      </c>
+      <c r="F62">
+        <v>0.0408176</v>
+      </c>
+      <c r="G62">
+        <v>0.03816730221194885</v>
+      </c>
+      <c r="H62">
+        <v>0.0433424</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63">
-        <v>3.8219999999999997E-2</v>
+        <v>0.03822</v>
       </c>
       <c r="B63">
-        <v>4.6679999999999999E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.04668</v>
+      </c>
+      <c r="C63">
+        <v>0.03780233848538477</v>
+      </c>
+      <c r="D63">
+        <v>0.0494808</v>
+      </c>
+      <c r="E63">
+        <v>0.03843616692232528</v>
+      </c>
+      <c r="F63">
+        <v>0.0452796</v>
+      </c>
+      <c r="G63">
+        <v>0.03849559663527548</v>
+      </c>
+      <c r="H63">
+        <v>0.0480804</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64">
-        <v>3.8539999999999998E-2</v>
+        <v>0.03854</v>
       </c>
       <c r="B64">
-        <v>5.1799999999999999E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.0518</v>
+      </c>
+      <c r="C64">
+        <v>0.03809371928095718</v>
+      </c>
+      <c r="D64">
+        <v>0.054908</v>
+      </c>
+      <c r="E64">
+        <v>0.03877097921678869</v>
+      </c>
+      <c r="F64">
+        <v>0.050246</v>
+      </c>
+      <c r="G64">
+        <v>0.03883448120129007</v>
+      </c>
+      <c r="H64">
+        <v>0.053354</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65">
-        <v>3.8899999999999997E-2</v>
+        <v>0.0389</v>
       </c>
       <c r="B65">
-        <v>5.7480000000000003E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.05748</v>
+      </c>
+      <c r="C65">
+        <v>0.03842152267597613</v>
+      </c>
+      <c r="D65">
+        <v>0.06092880000000001</v>
+      </c>
+      <c r="E65">
+        <v>0.03914764304806002</v>
+      </c>
+      <c r="F65">
+        <v>0.0557556</v>
+      </c>
+      <c r="G65">
+        <v>0.03921572633805648</v>
+      </c>
+      <c r="H65">
+        <v>0.0592044</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66">
-        <v>3.9300000000000002E-2</v>
+        <v>0.0393</v>
       </c>
       <c r="B66">
-        <v>6.3820000000000002E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.06382</v>
+      </c>
+      <c r="C66">
+        <v>0.03878574867044164</v>
+      </c>
+      <c r="D66">
+        <v>0.06764920000000001</v>
+      </c>
+      <c r="E66">
+        <v>0.03956615841613929</v>
+      </c>
+      <c r="F66">
+        <v>0.0619054</v>
+      </c>
+      <c r="G66">
+        <v>0.03963933204557474</v>
+      </c>
+      <c r="H66">
+        <v>0.0657346</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67">
-        <v>3.9739999999999998E-2</v>
+        <v>0.03974</v>
       </c>
       <c r="B67">
-        <v>7.0870000000000002E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.07087</v>
+      </c>
+      <c r="C67">
+        <v>0.03918639726435369</v>
+      </c>
+      <c r="D67">
+        <v>0.0751222</v>
+      </c>
+      <c r="E67">
+        <v>0.04002652532102645</v>
+      </c>
+      <c r="F67">
+        <v>0.0687439</v>
+      </c>
+      <c r="G67">
+        <v>0.0401052983238448</v>
+      </c>
+      <c r="H67">
+        <v>0.07299610000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68">
-        <v>4.02E-2</v>
+        <v>0.0402</v>
       </c>
       <c r="B68">
-        <v>7.8719999999999998E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.07872</v>
+      </c>
+      <c r="C68">
+        <v>0.03960525715798903</v>
+      </c>
+      <c r="D68">
+        <v>0.08344320000000001</v>
+      </c>
+      <c r="E68">
+        <v>0.0405078179943176</v>
+      </c>
+      <c r="F68">
+        <v>0.07635839999999999</v>
+      </c>
+      <c r="G68">
+        <v>0.04059244488749078</v>
+      </c>
+      <c r="H68">
+        <v>0.0810816</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69">
-        <v>4.0750000000000001E-2</v>
+        <v>0.04075</v>
       </c>
       <c r="B69">
-        <v>8.7499999999999994E-2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="C69">
+        <v>0.0401060679003791</v>
+      </c>
+      <c r="D69">
+        <v>0.09275</v>
+      </c>
+      <c r="E69">
+        <v>0.04108327662542657</v>
+      </c>
+      <c r="F69">
+        <v>0.08487499999999999</v>
+      </c>
+      <c r="G69">
+        <v>0.04117490273532837</v>
+      </c>
+      <c r="H69">
+        <v>0.090125</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70">
-        <v>4.1450000000000001E-2</v>
+        <v>0.04145</v>
       </c>
       <c r="B70">
-        <v>9.7390000000000004E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.09739</v>
+      </c>
+      <c r="C70">
+        <v>0.04074346339069373</v>
+      </c>
+      <c r="D70">
+        <v>0.1032334</v>
+      </c>
+      <c r="E70">
+        <v>0.04181567851956526</v>
+      </c>
+      <c r="F70">
+        <v>0.09446830000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.04191621272348529</v>
+      </c>
+      <c r="H70">
+        <v>0.1003117</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71">
-        <v>4.2349999999999999E-2</v>
+        <v>0.04235</v>
       </c>
       <c r="B71">
-        <v>0.10847999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.10848</v>
+      </c>
+      <c r="C71">
+        <v>0.04156297187824112</v>
+      </c>
+      <c r="D71">
+        <v>0.1149888</v>
+      </c>
+      <c r="E71">
+        <v>0.04275733809774358</v>
+      </c>
+      <c r="F71">
+        <v>0.1052256</v>
+      </c>
+      <c r="G71">
+        <v>0.04286932556540134</v>
+      </c>
+      <c r="H71">
+        <v>0.1117344</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72">
-        <v>4.333E-2</v>
+        <v>0.04333</v>
       </c>
       <c r="B72">
-        <v>0.12089999999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.1209</v>
+      </c>
+      <c r="C72">
+        <v>0.04245532556468161</v>
+      </c>
+      <c r="D72">
+        <v>0.128154</v>
+      </c>
+      <c r="E72">
+        <v>0.04378270074953776</v>
+      </c>
+      <c r="F72">
+        <v>0.117273</v>
+      </c>
+      <c r="G72">
+        <v>0.04390715954882102</v>
+      </c>
+      <c r="H72">
+        <v>0.124527</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73">
-        <v>4.4339999999999997E-2</v>
+        <v>0.04434</v>
       </c>
       <c r="B73">
         <v>0.13466</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C73">
+        <v>0.04337499620070701</v>
+      </c>
+      <c r="D73">
+        <v>0.1427396</v>
+      </c>
+      <c r="E73">
+        <v>0.04483945205393786</v>
+      </c>
+      <c r="F73">
+        <v>0.1306202</v>
+      </c>
+      <c r="G73">
+        <v>0.0449767639603046</v>
+      </c>
+      <c r="H73">
+        <v>0.1386998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74">
-        <v>4.555E-2</v>
+        <v>0.04555</v>
       </c>
       <c r="B74">
         <v>0.15026</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C74">
+        <v>0.04447677983396516</v>
+      </c>
+      <c r="D74">
+        <v>0.1592756</v>
+      </c>
+      <c r="E74">
+        <v>0.04610546104237762</v>
+      </c>
+      <c r="F74">
+        <v>0.1457522</v>
+      </c>
+      <c r="G74">
+        <v>0.04625817122554728</v>
+      </c>
+      <c r="H74">
+        <v>0.1547678</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75">
-        <v>4.6550000000000001E-2</v>
+        <v>0.04655</v>
       </c>
       <c r="B75">
         <v>0.16721</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C75">
+        <v>0.04538734482012893</v>
+      </c>
+      <c r="D75">
+        <v>0.1772426</v>
+      </c>
+      <c r="E75">
+        <v>0.04715174946257576</v>
+      </c>
+      <c r="F75">
+        <v>0.1621937</v>
+      </c>
+      <c r="G75">
+        <v>0.04731718549434288</v>
+      </c>
+      <c r="H75">
+        <v>0.1722263</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76">
-        <v>4.7600000000000003E-2</v>
+        <v>0.0476</v>
       </c>
       <c r="B76">
-        <v>0.18601999999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.18602</v>
+      </c>
+      <c r="C76">
+        <v>0.04634343805560088</v>
+      </c>
+      <c r="D76">
+        <v>0.1971812</v>
+      </c>
+      <c r="E76">
+        <v>0.0482503523037838</v>
+      </c>
+      <c r="F76">
+        <v>0.1804394</v>
+      </c>
+      <c r="G76">
+        <v>0.04842915047657827</v>
+      </c>
+      <c r="H76">
+        <v>0.1916006</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77">
-        <v>4.8719999999999999E-2</v>
+        <v>0.04872</v>
       </c>
       <c r="B77">
-        <v>0.20696999999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.20697</v>
+      </c>
+      <c r="C77">
+        <v>0.04736327084010429</v>
+      </c>
+      <c r="D77">
+        <v>0.2193882</v>
+      </c>
+      <c r="E77">
+        <v>0.0494221953344057</v>
+      </c>
+      <c r="F77">
+        <v>0.2007609</v>
+      </c>
+      <c r="G77">
+        <v>0.04961524645762935</v>
+      </c>
+      <c r="H77">
+        <v>0.2131791</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78">
-        <v>4.9910000000000003E-2</v>
+        <v>0.04991</v>
       </c>
       <c r="B78">
-        <v>0.23033000000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.23033</v>
+      </c>
+      <c r="C78">
+        <v>0.04844684317363918</v>
+      </c>
+      <c r="D78">
+        <v>0.2441498</v>
+      </c>
+      <c r="E78">
+        <v>0.05066727855444149</v>
+      </c>
+      <c r="F78">
+        <v>0.2234201</v>
+      </c>
+      <c r="G78">
+        <v>0.05087547343749613</v>
+      </c>
+      <c r="H78">
+        <v>0.2372399</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79">
-        <v>5.1209999999999999E-2</v>
+        <v>0.05121</v>
       </c>
       <c r="B79">
-        <v>0.25634000000000001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.25634</v>
+      </c>
+      <c r="C79">
+        <v>0.04963057765565206</v>
+      </c>
+      <c r="D79">
+        <v>0.2717204</v>
+      </c>
+      <c r="E79">
+        <v>0.05202745350069907</v>
+      </c>
+      <c r="F79">
+        <v>0.2486498</v>
+      </c>
+      <c r="G79">
+        <v>0.0522521919869304</v>
+      </c>
+      <c r="H79">
+        <v>0.2640302</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80">
-        <v>5.2589999999999998E-2</v>
+        <v>0.05259</v>
       </c>
       <c r="B80">
-        <v>0.28538999999999998</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.28539</v>
+      </c>
+      <c r="C80">
+        <v>0.05088715733655805</v>
+      </c>
+      <c r="D80">
+        <v>0.3025134</v>
+      </c>
+      <c r="E80">
+        <v>0.0534713315205725</v>
+      </c>
+      <c r="F80">
+        <v>0.2768283</v>
+      </c>
+      <c r="G80">
+        <v>0.05371363167786834</v>
+      </c>
+      <c r="H80">
+        <v>0.2939517</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81">
-        <v>5.416E-2</v>
+        <v>0.05416</v>
       </c>
       <c r="B81">
-        <v>0.31768000000000002</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.31768</v>
+      </c>
+      <c r="C81">
+        <v>0.05231674436483516</v>
+      </c>
+      <c r="D81">
+        <v>0.3367408000000001</v>
+      </c>
+      <c r="E81">
+        <v>0.05511400434028356</v>
+      </c>
+      <c r="F81">
+        <v>0.3081496</v>
+      </c>
+      <c r="G81">
+        <v>0.05537628407987744</v>
+      </c>
+      <c r="H81">
+        <v>0.3272104</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82">
-        <v>5.5789999999999999E-2</v>
+        <v>0.05579</v>
       </c>
       <c r="B82">
         <v>0.35385</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C82">
+        <v>0.05380096529228209</v>
+      </c>
+      <c r="D82">
+        <v>0.375081</v>
+      </c>
+      <c r="E82">
+        <v>0.05681945446520652</v>
+      </c>
+      <c r="F82">
+        <v>0.3432345</v>
+      </c>
+      <c r="G82">
+        <v>0.05710247733801428</v>
+      </c>
+      <c r="H82">
+        <v>0.3644655</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83">
-        <v>5.765E-2</v>
+        <v>0.05765</v>
       </c>
       <c r="B83">
-        <v>0.39406999999999998</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0.39407</v>
+      </c>
+      <c r="C83">
+        <v>0.0554946161665467</v>
+      </c>
+      <c r="D83">
+        <v>0.4177142</v>
+      </c>
+      <c r="E83">
+        <v>0.05876555092677505</v>
+      </c>
+      <c r="F83">
+        <v>0.3822479</v>
+      </c>
+      <c r="G83">
+        <v>0.05907224387797411</v>
+      </c>
+      <c r="H83">
+        <v>0.4058921</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84">
-        <v>5.9610000000000003E-2</v>
+        <v>0.05961</v>
       </c>
       <c r="B84">
         <v>0.43911</v>
       </c>
+      <c r="C84">
+        <v>0.05727932353942768</v>
+      </c>
+      <c r="D84">
+        <v>0.4654566</v>
+      </c>
+      <c r="E84">
+        <v>0.0608162762303634</v>
+      </c>
+      <c r="F84">
+        <v>0.4259367</v>
+      </c>
+      <c r="G84">
+        <v>0.06114791184481351</v>
+      </c>
+      <c r="H84">
+        <v>0.4522833</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>